--- a/evaluation/scifact/scifact_deepseek-chat_answers.xlsx
+++ b/evaluation/scifact/scifact_deepseek-chat_answers.xlsx
@@ -5567,7 +5567,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5604,6 +5604,13 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -5668,7 +5675,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5912,10 +5919,10 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
     </row>
@@ -5959,7 +5966,7 @@
       <c r="M2" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="N2" s="0" t="n">
+      <c r="N2" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6003,7 +6010,7 @@
       <c r="M3" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="N3" s="0" t="n">
+      <c r="N3" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6047,7 +6054,7 @@
       <c r="M4" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="N4" s="0" t="n">
+      <c r="N4" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6091,7 +6098,7 @@
       <c r="M5" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="N5" s="0" t="n">
+      <c r="N5" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6135,7 +6142,7 @@
       <c r="M6" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="N6" s="0" t="n">
+      <c r="N6" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6179,7 +6186,7 @@
       <c r="M7" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="N7" s="0" t="n">
+      <c r="N7" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6223,7 +6230,7 @@
       <c r="M8" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="N8" s="0" t="n">
+      <c r="N8" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6267,7 +6274,7 @@
       <c r="M9" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="N9" s="0" t="n">
+      <c r="N9" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6311,7 +6318,7 @@
       <c r="M10" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="N10" s="0" t="n">
+      <c r="N10" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6355,7 +6362,7 @@
       <c r="M11" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="N11" s="0" t="n">
+      <c r="N11" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6399,7 +6406,7 @@
       <c r="M12" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="N12" s="0" t="n">
+      <c r="N12" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6443,7 +6450,7 @@
       <c r="M13" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="N13" s="0" t="n">
+      <c r="N13" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6487,7 +6494,7 @@
       <c r="M14" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="N14" s="0" t="n">
+      <c r="N14" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6531,7 +6538,7 @@
       <c r="M15" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="N15" s="0" t="n">
+      <c r="N15" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6575,7 +6582,7 @@
       <c r="M16" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="N16" s="0" t="n">
+      <c r="N16" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6619,7 +6626,7 @@
       <c r="M17" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="N17" s="0" t="n">
+      <c r="N17" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6663,7 +6670,7 @@
       <c r="M18" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="N18" s="0" t="n">
+      <c r="N18" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6707,7 +6714,7 @@
       <c r="M19" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="N19" s="0" t="n">
+      <c r="N19" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6751,7 +6758,7 @@
       <c r="M20" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="N20" s="0" t="n">
+      <c r="N20" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6795,7 +6802,7 @@
       <c r="M21" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="N21" s="0" t="n">
+      <c r="N21" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6839,7 +6846,7 @@
       <c r="M22" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="N22" s="0" t="n">
+      <c r="N22" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6883,7 +6890,7 @@
       <c r="M23" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="N23" s="0" t="n">
+      <c r="N23" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6927,7 +6934,7 @@
       <c r="M24" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="N24" s="0" t="n">
+      <c r="N24" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6971,7 +6978,7 @@
       <c r="M25" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="N25" s="0" t="n">
+      <c r="N25" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7015,7 +7022,7 @@
       <c r="M26" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="N26" s="0" t="n">
+      <c r="N26" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7059,7 +7066,7 @@
       <c r="M27" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="N27" s="0" t="n">
+      <c r="N27" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7103,7 +7110,7 @@
       <c r="M28" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="N28" s="0" t="n">
+      <c r="N28" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7147,7 +7154,7 @@
       <c r="M29" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="N29" s="0" t="n">
+      <c r="N29" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7191,7 +7198,7 @@
       <c r="M30" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="N30" s="0" t="n">
+      <c r="N30" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7235,7 +7242,7 @@
       <c r="M31" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="N31" s="0" t="n">
+      <c r="N31" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7279,7 +7286,7 @@
       <c r="M32" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="N32" s="0" t="n">
+      <c r="N32" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7323,7 +7330,7 @@
       <c r="M33" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="N33" s="0" t="n">
+      <c r="N33" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7367,7 +7374,7 @@
       <c r="M34" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="N34" s="0" t="n">
+      <c r="N34" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7411,7 +7418,7 @@
       <c r="M35" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="N35" s="0" t="n">
+      <c r="N35" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7455,7 +7462,7 @@
       <c r="M36" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="N36" s="0" t="n">
+      <c r="N36" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7499,7 +7506,7 @@
       <c r="M37" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="N37" s="0" t="n">
+      <c r="N37" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7543,7 +7550,7 @@
       <c r="M38" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="N38" s="0" t="n">
+      <c r="N38" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7587,7 +7594,7 @@
       <c r="M39" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="N39" s="0" t="n">
+      <c r="N39" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7631,7 +7638,7 @@
       <c r="M40" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="N40" s="0" t="n">
+      <c r="N40" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7675,7 +7682,7 @@
       <c r="M41" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="N41" s="0" t="n">
+      <c r="N41" s="4" t="n">
         <v>1</v>
       </c>
     </row>
